--- a/projetos/fachada-sao-camilo/orcamento/PLANILHA_CLIENTE_Sao_Camilo_PREENCHIDA.xlsx
+++ b/projetos/fachada-sao-camilo/orcamento/PLANILHA_CLIENTE_Sao_Camilo_PREENCHIDA.xlsx
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="146" t="n">
-        <v>364</v>
+        <v>732.99</v>
       </c>
       <c r="H17" s="146">
         <f>F17+G17</f>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="146" t="n">
-        <v>364</v>
+        <v>732.99</v>
       </c>
       <c r="H18" s="146">
         <f>F18+G18</f>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="146" t="n">
-        <v>364</v>
+        <v>732.99</v>
       </c>
       <c r="H19" s="146">
         <f>F19+G19</f>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="146" t="n">
-        <v>364</v>
+        <v>732.99</v>
       </c>
       <c r="H20" s="146">
         <f>F20+G20</f>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="146" t="n">
-        <v>7800</v>
+        <v>15706.89</v>
       </c>
       <c r="H21" s="146">
         <f>F21+G21</f>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="146" t="n">
-        <v>1170</v>
+        <v>2356.03</v>
       </c>
       <c r="H22" s="146">
         <f>F22+G22</f>
@@ -2061,7 +2061,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="146" t="n">
-        <v>50180</v>
+        <v>101047.68</v>
       </c>
       <c r="G23" s="146" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="146" t="n">
-        <v>71500</v>
+        <v>143966.69</v>
       </c>
       <c r="H24" s="146">
         <f>F24+G24</f>
@@ -2267,10 +2267,10 @@
         <v>1884.25</v>
       </c>
       <c r="F29" s="146" t="n">
-        <v>2.97</v>
+        <v>5.99</v>
       </c>
       <c r="G29" s="146" t="n">
-        <v>116.94</v>
+        <v>235.49</v>
       </c>
       <c r="H29" s="146">
         <f>F29+G29</f>
@@ -2320,10 +2320,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="146" t="n">
-        <v>20280</v>
+        <v>40837.92</v>
       </c>
       <c r="G30" s="146" t="n">
-        <v>10140</v>
+        <v>20418.96</v>
       </c>
       <c r="H30" s="146">
         <f>F30+G30</f>
@@ -2369,10 +2369,10 @@
         <v>1</v>
       </c>
       <c r="F31" s="146" t="n">
-        <v>1287</v>
+        <v>2591.64</v>
       </c>
       <c r="G31" s="146" t="n">
-        <v>3250</v>
+        <v>6544.54</v>
       </c>
       <c r="H31" s="146">
         <f>F31+G31</f>
@@ -2414,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="146" t="n">
-        <v>585</v>
+        <v>1178.02</v>
       </c>
       <c r="G32" s="146" t="n">
-        <v>13000</v>
+        <v>26178.16</v>
       </c>
       <c r="H32" s="146">
         <f>F32+G32</f>
@@ -2459,10 +2459,10 @@
         <v>1</v>
       </c>
       <c r="F33" s="146" t="n">
-        <v>975</v>
+        <v>1963.36</v>
       </c>
       <c r="G33" s="146" t="n">
-        <v>15600</v>
+        <v>31413.79</v>
       </c>
       <c r="H33" s="146">
         <f>F33+G33</f>
@@ -2508,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="146" t="n">
-        <v>8112</v>
+        <v>16335.17</v>
       </c>
       <c r="G34" s="146" t="n">
         <v>0</v>
@@ -2773,10 +2773,10 @@
         <v>50</v>
       </c>
       <c r="F43" s="153" t="n">
-        <v>65.78</v>
+        <v>132.46</v>
       </c>
       <c r="G43" s="153" t="n">
-        <v>650</v>
+        <v>1308.91</v>
       </c>
       <c r="H43" s="153">
         <f>F43+G43</f>
@@ -2818,10 +2818,10 @@
         <v>11</v>
       </c>
       <c r="F44" s="153" t="n">
-        <v>1857.94</v>
+        <v>3741.33</v>
       </c>
       <c r="G44" s="153" t="n">
-        <v>156</v>
+        <v>314.14</v>
       </c>
       <c r="H44" s="153">
         <f>F44+G44</f>
@@ -2863,10 +2863,10 @@
         <v>5</v>
       </c>
       <c r="F45" s="153" t="n">
-        <v>958.88</v>
+        <v>1930.9</v>
       </c>
       <c r="G45" s="153" t="n">
-        <v>156</v>
+        <v>314.14</v>
       </c>
       <c r="H45" s="153">
         <f>F45+G45</f>
@@ -2908,10 +2908,10 @@
         <v>80</v>
       </c>
       <c r="F46" s="153" t="n">
-        <v>763.33</v>
+        <v>1537.12</v>
       </c>
       <c r="G46" s="153" t="n">
-        <v>585</v>
+        <v>1178.02</v>
       </c>
       <c r="H46" s="153">
         <f>F46+G46</f>
@@ -2961,10 +2961,10 @@
         <v>110</v>
       </c>
       <c r="F47" s="153" t="n">
-        <v>1021.54</v>
+        <v>2057.08</v>
       </c>
       <c r="G47" s="153" t="n">
-        <v>156</v>
+        <v>314.14</v>
       </c>
       <c r="H47" s="153">
         <f>F47+G47</f>
@@ -3112,10 +3112,10 @@
         <v>16</v>
       </c>
       <c r="F52" s="146" t="n">
-        <v>130</v>
+        <v>261.78</v>
       </c>
       <c r="G52" s="146" t="n">
-        <v>45.5</v>
+        <v>91.62</v>
       </c>
       <c r="H52" s="146">
         <f>F52+G52</f>
@@ -3158,10 +3158,10 @@
         <v>22</v>
       </c>
       <c r="F53" s="146" t="n">
-        <v>130</v>
+        <v>261.78</v>
       </c>
       <c r="G53" s="146" t="n">
-        <v>45.5</v>
+        <v>91.62</v>
       </c>
       <c r="H53" s="146">
         <f>F53+G53</f>
@@ -3203,10 +3203,10 @@
         <v>14</v>
       </c>
       <c r="F54" s="146" t="n">
-        <v>130</v>
+        <v>261.78</v>
       </c>
       <c r="G54" s="146" t="n">
-        <v>45.5</v>
+        <v>91.62</v>
       </c>
       <c r="H54" s="146">
         <f>F54+G54</f>
@@ -3311,10 +3311,10 @@
         <v>1</v>
       </c>
       <c r="F57" s="146" t="n">
-        <v>695.5</v>
+        <v>1400.53</v>
       </c>
       <c r="G57" s="146" t="n">
-        <v>2600</v>
+        <v>5235.63</v>
       </c>
       <c r="H57" s="146">
         <f>F57+G57</f>
@@ -3364,10 +3364,10 @@
         <v>1</v>
       </c>
       <c r="F58" s="146" t="n">
-        <v>904.8</v>
+        <v>1822</v>
       </c>
       <c r="G58" s="146" t="n">
-        <v>2600</v>
+        <v>5235.63</v>
       </c>
       <c r="H58" s="146">
         <f>F58+G58</f>
@@ -3417,10 +3417,10 @@
         <v>1</v>
       </c>
       <c r="F59" s="146" t="n">
-        <v>10860.2</v>
+        <v>21869.23</v>
       </c>
       <c r="G59" s="146" t="n">
-        <v>59150</v>
+        <v>119110.61</v>
       </c>
       <c r="H59" s="146">
         <f>F59+G59</f>
@@ -3466,10 +3466,10 @@
         <v>1</v>
       </c>
       <c r="F60" s="146" t="n">
-        <v>1332.5</v>
+        <v>2683.26</v>
       </c>
       <c r="G60" s="146" t="n">
-        <v>5850</v>
+        <v>11780.17</v>
       </c>
       <c r="H60" s="146">
         <f>F60+G60</f>
@@ -3631,10 +3631,10 @@
         <v>1830.4</v>
       </c>
       <c r="F65" s="146" t="n">
-        <v>86.86</v>
+        <v>174.92</v>
       </c>
       <c r="G65" s="146" t="n">
-        <v>340.5</v>
+        <v>685.66</v>
       </c>
       <c r="H65" s="146">
         <f>F65+G65</f>
@@ -3676,10 +3676,10 @@
         <v>53.83</v>
       </c>
       <c r="F66" s="146" t="n">
-        <v>96.59999999999999</v>
+        <v>194.52</v>
       </c>
       <c r="G66" s="146" t="n">
-        <v>340.49</v>
+        <v>685.65</v>
       </c>
       <c r="H66" s="146">
         <f>F66+G66</f>
@@ -3721,10 +3721,10 @@
         <v>2</v>
       </c>
       <c r="F67" s="146" t="n">
-        <v>940.55</v>
+        <v>1893.99</v>
       </c>
       <c r="G67" s="146" t="n">
-        <v>340.6</v>
+        <v>685.87</v>
       </c>
       <c r="H67" s="146">
         <f>F67+G67</f>
@@ -3766,10 +3766,10 @@
         <v>1269</v>
       </c>
       <c r="F68" s="146" t="n">
-        <v>39.3</v>
+        <v>79.13</v>
       </c>
       <c r="G68" s="146" t="n">
-        <v>32.5</v>
+        <v>65.45</v>
       </c>
       <c r="H68" s="146">
         <f>F68+G68</f>
@@ -3815,10 +3815,10 @@
         <v>287.84</v>
       </c>
       <c r="F69" s="146" t="n">
-        <v>372.2</v>
+        <v>749.49</v>
       </c>
       <c r="G69" s="146" t="n">
-        <v>195</v>
+        <v>392.67</v>
       </c>
       <c r="H69" s="146">
         <f>F69+G69</f>
@@ -3860,10 +3860,10 @@
         <v>23.47</v>
       </c>
       <c r="F70" s="146" t="n">
-        <v>379.75</v>
+        <v>764.71</v>
       </c>
       <c r="G70" s="146" t="n">
-        <v>195.03</v>
+        <v>392.73</v>
       </c>
       <c r="H70" s="146">
         <f>F70+G70</f>
@@ -4026,10 +4026,10 @@
         <v>3</v>
       </c>
       <c r="F75" s="146" t="n">
-        <v>777.4</v>
+        <v>1565.45</v>
       </c>
       <c r="G75" s="146" t="n">
-        <v>650</v>
+        <v>1308.91</v>
       </c>
       <c r="H75" s="146">
         <f>F75+G75</f>
@@ -4305,10 +4305,10 @@
         <v>1884.25</v>
       </c>
       <c r="F84" s="146" t="n">
-        <v>107.94</v>
+        <v>217.35</v>
       </c>
       <c r="G84" s="146" t="n">
-        <v>83.2</v>
+        <v>167.54</v>
       </c>
       <c r="H84" s="146">
         <f>F84+G84</f>
@@ -4651,10 +4651,10 @@
         <v>220</v>
       </c>
       <c r="F95" s="146" t="n">
-        <v>246.05</v>
+        <v>495.47</v>
       </c>
       <c r="G95" s="146" t="n">
-        <v>73.39</v>
+        <v>147.79</v>
       </c>
       <c r="H95" s="146">
         <f>F95+G95</f>
@@ -4760,10 +4760,10 @@
         <v>10</v>
       </c>
       <c r="F98" s="146" t="n">
-        <v>455</v>
+        <v>916.24</v>
       </c>
       <c r="G98" s="146" t="n">
-        <v>780</v>
+        <v>1570.69</v>
       </c>
       <c r="H98" s="146">
         <f>F98+G98</f>
@@ -4809,10 +4809,10 @@
         <v>37</v>
       </c>
       <c r="F99" s="146" t="n">
-        <v>134.04</v>
+        <v>269.92</v>
       </c>
       <c r="G99" s="146" t="n">
-        <v>52</v>
+        <v>104.71</v>
       </c>
       <c r="H99" s="146">
         <f>F99+G99</f>
@@ -4858,10 +4858,10 @@
         <v>1</v>
       </c>
       <c r="F100" s="146" t="n">
-        <v>10166</v>
+        <v>20471.32</v>
       </c>
       <c r="G100" s="146" t="n">
-        <v>13000</v>
+        <v>26178.16</v>
       </c>
       <c r="H100" s="146">
         <f>F100+G100</f>
@@ -4907,10 +4907,10 @@
         <v>1</v>
       </c>
       <c r="F101" s="146" t="n">
-        <v>650</v>
+        <v>1308.91</v>
       </c>
       <c r="G101" s="146" t="n">
-        <v>3900</v>
+        <v>7853.45</v>
       </c>
       <c r="H101" s="146">
         <f>F101+G101</f>
@@ -4956,10 +4956,10 @@
         <v>1</v>
       </c>
       <c r="F102" s="146" t="n">
-        <v>1950</v>
+        <v>3926.72</v>
       </c>
       <c r="G102" s="146" t="n">
-        <v>5200</v>
+        <v>10471.26</v>
       </c>
       <c r="H102" s="146">
         <f>F102+G102</f>
@@ -5005,10 +5005,10 @@
         <v>1</v>
       </c>
       <c r="F103" s="146" t="n">
-        <v>1040</v>
+        <v>2094.25</v>
       </c>
       <c r="G103" s="146" t="n">
-        <v>3250</v>
+        <v>6544.54</v>
       </c>
       <c r="H103" s="146">
         <f>F103+G103</f>
@@ -5054,10 +5054,10 @@
         <v>80</v>
       </c>
       <c r="F104" s="146" t="n">
-        <v>101.4</v>
+        <v>204.19</v>
       </c>
       <c r="G104" s="146" t="n">
-        <v>67.59999999999999</v>
+        <v>136.13</v>
       </c>
       <c r="H104" s="146">
         <f>F104+G104</f>
@@ -5106,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="146" t="n">
-        <v>13</v>
+        <v>26.18</v>
       </c>
       <c r="H105" s="146">
         <f>F105+G105</f>
@@ -5152,7 +5152,7 @@
         <v>1</v>
       </c>
       <c r="F106" s="146" t="n">
-        <v>265712.2</v>
+        <v>535065.79</v>
       </c>
       <c r="G106" s="146" t="n">
         <v>0</v>
@@ -5201,10 +5201,10 @@
         <v>212</v>
       </c>
       <c r="F107" s="146" t="n">
-        <v>114</v>
+        <v>229.55</v>
       </c>
       <c r="G107" s="146" t="n">
-        <v>71.5</v>
+        <v>143.98</v>
       </c>
       <c r="H107" s="146">
         <f>F107+G107</f>
@@ -5250,10 +5250,10 @@
         <v>165</v>
       </c>
       <c r="F108" s="146" t="n">
-        <v>62.83</v>
+        <v>126.53</v>
       </c>
       <c r="G108" s="146" t="n">
-        <v>52</v>
+        <v>104.71</v>
       </c>
       <c r="H108" s="146">
         <f>F108+G108</f>
@@ -5299,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="146" t="n">
-        <v>34190</v>
+        <v>68848.55</v>
       </c>
       <c r="G109" s="146" t="n">
         <v>0</v>
@@ -5348,10 +5348,10 @@
         <v>17</v>
       </c>
       <c r="F110" s="146" t="n">
-        <v>58.5</v>
+        <v>117.8</v>
       </c>
       <c r="G110" s="146" t="n">
-        <v>32.5</v>
+        <v>65.45</v>
       </c>
       <c r="H110" s="146">
         <f>F110+G110</f>
@@ -5397,10 +5397,10 @@
         <v>1</v>
       </c>
       <c r="F111" s="146" t="n">
-        <v>3250</v>
+        <v>6544.54</v>
       </c>
       <c r="G111" s="146" t="n">
-        <v>4550</v>
+        <v>9162.35</v>
       </c>
       <c r="H111" s="146">
         <f>F111+G111</f>
@@ -5510,10 +5510,10 @@
         <v>1</v>
       </c>
       <c r="F114" s="146" t="n">
-        <v>1300</v>
+        <v>2617.82</v>
       </c>
       <c r="G114" s="146" t="n">
-        <v>10400</v>
+        <v>20942.52</v>
       </c>
       <c r="H114" s="146">
         <f>F114+G114</f>
@@ -5555,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="F115" s="146" t="n">
-        <v>7644</v>
+        <v>15392.76</v>
       </c>
       <c r="G115" s="146" t="n">
-        <v>1950</v>
+        <v>3926.72</v>
       </c>
       <c r="H115" s="146">
         <f>F115+G115</f>
@@ -5600,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="146" t="n">
-        <v>2264.6</v>
+        <v>4560.23</v>
       </c>
       <c r="G116" s="146" t="n">
         <v>0</v>
